--- a/artfynd/A 22535-2026 artfynd.xlsx
+++ b/artfynd/A 22535-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3261,6 +3261,580 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>133871987</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57145</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Masteråsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>605065</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6665503</v>
+      </c>
+      <c r="S25" t="n">
+        <v>23</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Uppflygande</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>133871989</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97999</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Masteråsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>605130</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6665434</v>
+      </c>
+      <c r="S26" t="n">
+        <v>21</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>133871984</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58119</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Masteråsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>604903</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6665565</v>
+      </c>
+      <c r="S27" t="n">
+        <v>19</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>133871985</v>
+      </c>
+      <c r="B28" t="n">
+        <v>106262</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Masteråsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>604910</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6665659</v>
+      </c>
+      <c r="S28" t="n">
+        <v>33</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>133871986</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57145</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Masteråsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>605008</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6665552</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22535-2026 artfynd.xlsx
+++ b/artfynd/A 22535-2026 artfynd.xlsx
@@ -3390,7 +3390,7 @@
         <v>133871989</v>
       </c>
       <c r="B26" t="n">
-        <v>97999</v>
+        <v>98003</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>133871985</v>
       </c>
       <c r="B28" t="n">
-        <v>106262</v>
+        <v>106266</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 22535-2026 artfynd.xlsx
+++ b/artfynd/A 22535-2026 artfynd.xlsx
@@ -3390,7 +3390,7 @@
         <v>133871989</v>
       </c>
       <c r="B26" t="n">
-        <v>98003</v>
+        <v>98005</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>133871985</v>
       </c>
       <c r="B28" t="n">
-        <v>106266</v>
+        <v>106268</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 22535-2026 artfynd.xlsx
+++ b/artfynd/A 22535-2026 artfynd.xlsx
@@ -3263,10 +3263,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133871987</v>
+        <v>133871989</v>
       </c>
       <c r="B25" t="n">
-        <v>57145</v>
+        <v>98033</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3274,49 +3274,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Masteråsen, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>605065</v>
+        <v>605130</v>
       </c>
       <c r="R25" t="n">
-        <v>6665503</v>
+        <v>6665434</v>
       </c>
       <c r="S25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3345,7 +3333,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3355,12 +3343,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Uppflygande</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3387,10 +3370,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133871989</v>
+        <v>133871987</v>
       </c>
       <c r="B26" t="n">
-        <v>98005</v>
+        <v>57152</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3398,37 +3381,49 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Masteråsen, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>605130</v>
+        <v>605065</v>
       </c>
       <c r="R26" t="n">
-        <v>6665434</v>
+        <v>6665503</v>
       </c>
       <c r="S26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3457,7 +3452,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3467,7 +3462,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3497,7 +3497,7 @@
         <v>133871984</v>
       </c>
       <c r="B27" t="n">
-        <v>58119</v>
+        <v>58126</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>133871985</v>
       </c>
       <c r="B28" t="n">
-        <v>106268</v>
+        <v>106296</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>133871986</v>
       </c>
       <c r="B29" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 22535-2026 artfynd.xlsx
+++ b/artfynd/A 22535-2026 artfynd.xlsx
@@ -3266,7 +3266,7 @@
         <v>133871989</v>
       </c>
       <c r="B25" t="n">
-        <v>98033</v>
+        <v>98043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>133871987</v>
       </c>
       <c r="B26" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>133871984</v>
       </c>
       <c r="B27" t="n">
-        <v>58126</v>
+        <v>58136</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>133871985</v>
       </c>
       <c r="B28" t="n">
-        <v>106296</v>
+        <v>106306</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>133871986</v>
       </c>
       <c r="B29" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 22535-2026 artfynd.xlsx
+++ b/artfynd/A 22535-2026 artfynd.xlsx
@@ -3609,7 +3609,7 @@
         <v>133871985</v>
       </c>
       <c r="B28" t="n">
-        <v>106306</v>
+        <v>106307</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 22535-2026 artfynd.xlsx
+++ b/artfynd/A 22535-2026 artfynd.xlsx
@@ -3266,7 +3266,7 @@
         <v>133871989</v>
       </c>
       <c r="B25" t="n">
-        <v>98043</v>
+        <v>98045</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>133871985</v>
       </c>
       <c r="B28" t="n">
-        <v>106307</v>
+        <v>106309</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 22535-2026 artfynd.xlsx
+++ b/artfynd/A 22535-2026 artfynd.xlsx
@@ -3266,7 +3266,7 @@
         <v>133871989</v>
       </c>
       <c r="B25" t="n">
-        <v>98045</v>
+        <v>98046</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>133871985</v>
       </c>
       <c r="B28" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 22535-2026 artfynd.xlsx
+++ b/artfynd/A 22535-2026 artfynd.xlsx
@@ -3266,7 +3266,7 @@
         <v>133871989</v>
       </c>
       <c r="B25" t="n">
-        <v>98046</v>
+        <v>98053</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>133871985</v>
       </c>
       <c r="B28" t="n">
-        <v>106310</v>
+        <v>106317</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 22535-2026 artfynd.xlsx
+++ b/artfynd/A 22535-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69679628</v>
+        <v>69679442</v>
       </c>
       <c r="B2" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604820.1755299396</v>
+        <v>604872</v>
       </c>
       <c r="R2" t="n">
-        <v>6665792.853237213</v>
+        <v>6665801</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2017-10-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-10-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,19 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69679442</v>
+        <v>69679461</v>
       </c>
       <c r="B3" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604871.9044252828</v>
+        <v>604877</v>
       </c>
       <c r="R3" t="n">
-        <v>6665800.81417332</v>
+        <v>6665825</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2017-10-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-10-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>69679452</v>
+        <v>69679472</v>
       </c>
       <c r="B4" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604828.0153373674</v>
+        <v>604879</v>
       </c>
       <c r="R4" t="n">
-        <v>6665728.239639583</v>
+        <v>6665578</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2017-10-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-10-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,19 +966,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>69679855</v>
+        <v>69679736</v>
       </c>
       <c r="B5" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604902.0072650538</v>
+        <v>604871</v>
       </c>
       <c r="R5" t="n">
-        <v>6665708.906506974</v>
+        <v>6665802</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2017-10-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-10-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,19 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>69679736</v>
+        <v>69679855</v>
       </c>
       <c r="B6" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604870.8776125392</v>
+        <v>604902</v>
       </c>
       <c r="R6" t="n">
-        <v>6665801.782331687</v>
+        <v>6665709</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2017-10-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-10-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>69679836</v>
+        <v>69679392</v>
       </c>
       <c r="B7" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604855.1287342589</v>
+        <v>604834</v>
       </c>
       <c r="R7" t="n">
-        <v>6665740.983958775</v>
+        <v>6665735</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2017-10-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2017-10-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>69679677</v>
+        <v>69679402</v>
       </c>
       <c r="B8" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,21 +1285,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Heden 3, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604863.1328445488</v>
+        <v>604855</v>
       </c>
       <c r="R8" t="n">
-        <v>6665548.190313944</v>
+        <v>6665745</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,19 +1325,9 @@
           <t>2017-10-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2017-10-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>69679791</v>
+        <v>69679439</v>
       </c>
       <c r="B9" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1496,17 +1382,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Heden 3, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604749.0477394136</v>
+        <v>604937</v>
       </c>
       <c r="R9" t="n">
-        <v>6665921.990723005</v>
+        <v>6665371</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,19 +1426,9 @@
           <t>2017-10-07</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2017-10-07</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,15 +1455,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>69679503</v>
+        <v>69679452</v>
       </c>
       <c r="B10" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1615,10 +1490,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604846.1008046698</v>
+        <v>604828</v>
       </c>
       <c r="R10" t="n">
-        <v>6665742.222393428</v>
+        <v>6665728</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1648,19 +1523,9 @@
           <t>2017-10-07</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2017-10-07</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,15 +1552,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>69679545</v>
+        <v>69679503</v>
       </c>
       <c r="B11" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,10 +1587,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604751.0727966534</v>
+        <v>604846</v>
       </c>
       <c r="R11" t="n">
-        <v>6665921.051049338</v>
+        <v>6665742</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,19 +1620,9 @@
           <t>2017-10-07</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2017-10-07</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,15 +1649,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>69679392</v>
+        <v>69679517</v>
       </c>
       <c r="B12" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1839,10 +1684,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>604833.8205295254</v>
+        <v>604879</v>
       </c>
       <c r="R12" t="n">
-        <v>6665734.889189304</v>
+        <v>6665835</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,19 +1717,9 @@
           <t>2017-10-07</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2017-10-07</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1911,15 +1746,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>69679525</v>
+        <v>69679522</v>
       </c>
       <c r="B13" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,10 +1781,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>604860.236184763</v>
+        <v>604755</v>
       </c>
       <c r="R13" t="n">
-        <v>6665527.158830051</v>
+        <v>6665920</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1981,22 +1811,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2017-10-06</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2017-10-06</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,15 +1843,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>69679811</v>
+        <v>69679524</v>
       </c>
       <c r="B14" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2063,10 +1878,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>604852.1236835553</v>
+        <v>604859</v>
       </c>
       <c r="R14" t="n">
-        <v>6666056.096196506</v>
+        <v>6665718</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2096,19 +1911,9 @@
           <t>2017-10-07</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2017-10-07</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2135,15 +1940,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>69679517</v>
+        <v>69679525</v>
       </c>
       <c r="B15" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2175,10 +1975,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>604878.9231292588</v>
+        <v>604860</v>
       </c>
       <c r="R15" t="n">
-        <v>6665834.929138737</v>
+        <v>6665527</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2205,22 +2005,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2017-10-07</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2017-10-07</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,15 +2037,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>69679747</v>
+        <v>69679545</v>
       </c>
       <c r="B16" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2287,10 +2072,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>604834.9591617953</v>
+        <v>604751</v>
       </c>
       <c r="R16" t="n">
-        <v>6666149.860918853</v>
+        <v>6665921</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2320,19 +2105,9 @@
           <t>2017-10-07</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2017-10-07</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2359,15 +2134,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>69679472</v>
+        <v>69679628</v>
       </c>
       <c r="B17" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2375,21 +2145,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2399,10 +2169,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>604878.7667433978</v>
+        <v>604820</v>
       </c>
       <c r="R17" t="n">
-        <v>6665578.064667739</v>
+        <v>6665793</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2432,19 +2202,9 @@
           <t>2017-10-07</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2017-10-07</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2471,15 +2231,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>69679461</v>
+        <v>69679633</v>
       </c>
       <c r="B18" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,21 +2242,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2511,10 +2266,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>604877.2111734282</v>
+        <v>604867</v>
       </c>
       <c r="R18" t="n">
-        <v>6665824.90542171</v>
+        <v>6665666</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2544,19 +2299,9 @@
           <t>2017-10-07</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2017-10-07</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2583,15 +2328,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>69679402</v>
+        <v>69679647</v>
       </c>
       <c r="B19" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2616,17 +2356,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Heden 3, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>604855.0148741654</v>
+        <v>604902</v>
       </c>
       <c r="R19" t="n">
-        <v>6665744.970724155</v>
+        <v>6665716</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2656,19 +2400,9 @@
           <t>2017-10-07</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2017-10-07</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2695,15 +2429,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>69679633</v>
+        <v>69679677</v>
       </c>
       <c r="B20" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2728,17 +2457,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Heden 3, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>604866.7624684483</v>
+        <v>604863</v>
       </c>
       <c r="R20" t="n">
-        <v>6665666.003838937</v>
+        <v>6665548</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2768,19 +2501,9 @@
           <t>2017-10-07</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2017-10-07</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2807,15 +2530,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>69679524</v>
+        <v>69679747</v>
       </c>
       <c r="B21" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2847,10 +2565,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>604858.7785285772</v>
+        <v>604835</v>
       </c>
       <c r="R21" t="n">
-        <v>6665718.145513659</v>
+        <v>6666150</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2880,19 +2598,9 @@
           <t>2017-10-07</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2017-10-07</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2919,15 +2627,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>69679522</v>
+        <v>69679791</v>
       </c>
       <c r="B22" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2959,10 +2662,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>604755.0944759999</v>
+        <v>604749</v>
       </c>
       <c r="R22" t="n">
-        <v>6665920.168347797</v>
+        <v>6665922</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2992,19 +2695,9 @@
           <t>2017-10-07</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2017-10-07</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3031,15 +2724,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>69679647</v>
+        <v>69679811</v>
       </c>
       <c r="B23" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3064,21 +2752,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Heden 3, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>604901.8079214351</v>
+        <v>604852</v>
       </c>
       <c r="R23" t="n">
-        <v>6665715.883405142</v>
+        <v>6666056</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3108,19 +2792,9 @@
           <t>2017-10-07</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2017-10-07</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3147,15 +2821,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>69679439</v>
+        <v>69679836</v>
       </c>
       <c r="B24" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3180,21 +2849,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Heden 3, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>604937.1364718372</v>
+        <v>604855</v>
       </c>
       <c r="R24" t="n">
-        <v>6665371.238607372</v>
+        <v>6665741</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3224,19 +2889,9 @@
           <t>2017-10-07</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2017-10-07</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3263,10 +2918,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133871989</v>
+        <v>133871986</v>
       </c>
       <c r="B25" t="n">
-        <v>98053</v>
+        <v>57162</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3274,37 +2929,45 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Masteråsen, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>605130</v>
+        <v>605008</v>
       </c>
       <c r="R25" t="n">
-        <v>6665434</v>
+        <v>6665552</v>
       </c>
       <c r="S25" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3333,7 +2996,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3343,7 +3006,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3606,10 +3269,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133871985</v>
+        <v>133871991</v>
       </c>
       <c r="B28" t="n">
-        <v>106317</v>
+        <v>58131</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,31 +3280,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>103023</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3650,13 +3309,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>604910</v>
+        <v>605145</v>
       </c>
       <c r="R28" t="n">
-        <v>6665659</v>
+        <v>6665404</v>
       </c>
       <c r="S28" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3685,7 +3344,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3695,7 +3354,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3722,10 +3381,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133871986</v>
+        <v>133871985</v>
       </c>
       <c r="B29" t="n">
-        <v>57162</v>
+        <v>106324</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3733,45 +3392,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Masteråsen, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>605008</v>
+        <v>604910</v>
       </c>
       <c r="R29" t="n">
-        <v>6665552</v>
+        <v>6665659</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3800,7 +3460,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3810,7 +3470,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3834,6 +3494,327 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>133871988</v>
+      </c>
+      <c r="B30" t="n">
+        <v>106199</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221154</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skogsstjärna</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lysimachia europaea</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Masteråsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>605106</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6665457</v>
+      </c>
+      <c r="S30" t="n">
+        <v>21</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>133871989</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Masteråsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>605130</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6665434</v>
+      </c>
+      <c r="S31" t="n">
+        <v>21</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>133871993</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79057</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>228659</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Fönsterlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Cladonia stellaris</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Masteråsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>604918</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6665497</v>
+      </c>
+      <c r="S32" t="n">
+        <v>12</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22535-2026 artfynd.xlsx
+++ b/artfynd/A 22535-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69679442</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69679461</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69679472</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69679736</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69679855</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69679392</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69679402</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69679439</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69679452</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,6 +1696,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69679503</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1743,6 +1798,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69679517</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1840,6 +1900,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69679522</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1937,6 +2002,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69679524</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2034,6 +2104,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69679525</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2131,6 +2206,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69679545</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2228,6 +2308,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69679628</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2325,6 +2410,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69679633</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2426,6 +2516,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69679647</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2527,6 +2622,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69679677</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2624,6 +2724,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69679747</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2721,6 +2826,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69679791</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2818,6 +2928,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69679811</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2915,6 +3030,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69679836</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3030,6 +3150,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133871986</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3154,6 +3279,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133871987</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3266,6 +3396,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133871984</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3378,6 +3513,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133871991</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3494,6 +3634,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133871985</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3601,6 +3746,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133871988</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3708,6 +3858,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133871989</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3815,8 +3970,46 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133871993</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>